--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630501</v>
       </c>
       <c r="B2" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128630442</v>
       </c>
       <c r="B3" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128630466</v>
+        <v>128630446</v>
       </c>
       <c r="B4" t="n">
-        <v>86721</v>
+        <v>86901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3762</v>
+        <v>1988</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702296</v>
+        <v>702234</v>
       </c>
       <c r="R4" t="n">
-        <v>6666085</v>
+        <v>6666132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128630446</v>
+        <v>128630466</v>
       </c>
       <c r="B5" t="n">
-        <v>86895</v>
+        <v>86727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1988</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>702234</v>
+        <v>702296</v>
       </c>
       <c r="R5" t="n">
-        <v>6666132</v>
+        <v>6666085</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128630489</v>
       </c>
       <c r="B6" t="n">
-        <v>90891</v>
+        <v>90897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630501</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128630442</v>
       </c>
       <c r="B3" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128630446</v>
       </c>
       <c r="B4" t="n">
-        <v>86901</v>
+        <v>86903</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128630466</v>
       </c>
       <c r="B5" t="n">
-        <v>86727</v>
+        <v>86729</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128630489</v>
       </c>
       <c r="B6" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630501</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128630442</v>
       </c>
       <c r="B3" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128630489</v>
       </c>
       <c r="B6" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630501</v>
       </c>
       <c r="B2" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128630442</v>
       </c>
       <c r="B3" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128630446</v>
       </c>
       <c r="B4" t="n">
-        <v>86903</v>
+        <v>86930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128630466</v>
       </c>
       <c r="B5" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128630489</v>
       </c>
       <c r="B6" t="n">
-        <v>90900</v>
+        <v>90927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630501</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128630442</v>
       </c>
       <c r="B3" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128630446</v>
       </c>
       <c r="B4" t="n">
-        <v>86930</v>
+        <v>86934</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128630466</v>
       </c>
       <c r="B5" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128630489</v>
       </c>
       <c r="B6" t="n">
-        <v>90927</v>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630501</v>
       </c>
       <c r="B2" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128630442</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128630446</v>
       </c>
       <c r="B4" t="n">
-        <v>86934</v>
+        <v>86935</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128630489</v>
       </c>
       <c r="B6" t="n">
-        <v>90932</v>
+        <v>90937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630501</v>
       </c>
       <c r="B2" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128630442</v>
       </c>
       <c r="B3" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128630446</v>
       </c>
       <c r="B4" t="n">
-        <v>86935</v>
+        <v>86939</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128630466</v>
       </c>
       <c r="B5" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128630489</v>
       </c>
       <c r="B6" t="n">
-        <v>90937</v>
+        <v>90941</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630501</v>
       </c>
       <c r="B2" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128630442</v>
       </c>
       <c r="B3" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128630446</v>
       </c>
       <c r="B4" t="n">
-        <v>86939</v>
+        <v>86944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128630466</v>
       </c>
       <c r="B5" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128630489</v>
       </c>
       <c r="B6" t="n">
-        <v>90941</v>
+        <v>90946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630501</v>
       </c>
       <c r="B2" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128630442</v>
       </c>
       <c r="B3" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128630446</v>
       </c>
       <c r="B4" t="n">
-        <v>86946</v>
+        <v>86951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128630466</v>
       </c>
       <c r="B5" t="n">
-        <v>86771</v>
+        <v>86776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128630489</v>
       </c>
       <c r="B6" t="n">
-        <v>90948</v>
+        <v>90953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630501</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128630442</v>
       </c>
       <c r="B3" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128630446</v>
       </c>
       <c r="B4" t="n">
-        <v>86951</v>
+        <v>86957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128630466</v>
       </c>
       <c r="B5" t="n">
-        <v>86776</v>
+        <v>86782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128630489</v>
       </c>
       <c r="B6" t="n">
-        <v>90953</v>
+        <v>90959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630501</v>
       </c>
       <c r="B2" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128630442</v>
       </c>
       <c r="B3" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128630446</v>
       </c>
       <c r="B4" t="n">
-        <v>86957</v>
+        <v>86961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128630466</v>
       </c>
       <c r="B5" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128630489</v>
       </c>
       <c r="B6" t="n">
-        <v>90959</v>
+        <v>90963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128630501</v>
+        <v>128638087</v>
       </c>
       <c r="B2" t="n">
-        <v>92471</v>
+        <v>87289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>473</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702310</v>
+        <v>702265</v>
       </c>
       <c r="R2" t="n">
-        <v>6666041</v>
+        <v>6666022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128630442</v>
+        <v>128630446</v>
       </c>
       <c r="B3" t="n">
-        <v>92862</v>
+        <v>87322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>1988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702220</v>
+        <v>702234</v>
       </c>
       <c r="R3" t="n">
-        <v>6666144</v>
+        <v>6666132</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128630446</v>
+        <v>128630489</v>
       </c>
       <c r="B4" t="n">
-        <v>86961</v>
+        <v>91333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1988</v>
+        <v>2008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702234</v>
+        <v>702320</v>
       </c>
       <c r="R4" t="n">
-        <v>6666132</v>
+        <v>6666062</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128630466</v>
+        <v>128630525</v>
       </c>
       <c r="B5" t="n">
-        <v>86786</v>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>702296</v>
+        <v>702307</v>
       </c>
       <c r="R5" t="n">
-        <v>6666085</v>
+        <v>6666022</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128630489</v>
+        <v>128630521</v>
       </c>
       <c r="B6" t="n">
-        <v>90963</v>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2008</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>702320</v>
+        <v>702307</v>
       </c>
       <c r="R6" t="n">
-        <v>6666062</v>
+        <v>6666022</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,6 +1157,685 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128630466</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kyrksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>702296</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6666085</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128630501</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kyrksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>702310</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6666041</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128638097</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kyrksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>702265</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6666022</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128630442</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kyrksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>702220</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6666144</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128638096</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kyrksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>702265</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6666022</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128630537</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kyrksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>702307</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6666022</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128630586</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kyrksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>702307</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6666022</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1054-2022 artfynd.xlsx
+++ b/artfynd/A 1054-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128638087</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630446</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630489</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630525</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630521</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630466</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630501</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128638097</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630442</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128638096</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630537</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,8 +1896,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630586</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>